--- a/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:03:21+00:00</t>
+    <t>2026-09-10T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1539,7 +1539,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-allgemeine-kultur|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-kultur|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-allgemeine-bestimmung|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-bestimmung|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-keimzahl|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-empfindlichkeit|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-mikroskopie|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-antigen-antikoerper-quantitativ|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-aviditaet|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-ct-wert|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-titer|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-nugent-score|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-barlett-score|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-molekulare-pathogenlast|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-resistenzmechanismen-determinanten|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-virulenzfaktor|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-resistenzkategorie-status|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-mrgn-klasse|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-voraussichtliche-empfindlichkeit)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-allgemeine-kultur|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-kultur|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-allgemeine-bestimmung|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-bestimmung|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-keimzahl|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-empfindlichkeit|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-mikroskopie|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-mikroskopie|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-antigen-antikoerper-quantitativ|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-aviditaet|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-ct-wert|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-titer|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-nugent-score|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-bartlett-score|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-molekulare-pathogenlast|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-resistenzmechanismen-determinanten|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-virulenzfaktor|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-resistenzkategorie-status|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-mrgn-klasse|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-voraussichtliche-empfindlichkeit)
 </t>
   </si>
   <si>
@@ -1667,7 +1667,7 @@
 </t>
   </si>
   <si>
-    <t>Schlussfolgerung</t>
+    <t>Zusammenfassende Beurteilung des Labors im Freitext. Fuer serologische Befunde die tragende Stelle, weil sich die Diagnose dort erst aus der Zusammenschau mehrerer Einzelergebnisse ergibt.</t>
   </si>
   <si>
     <t>Klinische Schlussfolgerung/Interpretation der Testergebnisse</t>

--- a/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:05:40+00:00</t>
+    <t>2026-09-12T16:32:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1539,7 +1539,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-allgemeine-kultur|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-kultur|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-allgemeine-bestimmung|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-bestimmung|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-keimzahl|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-empfindlichkeit|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-mikroskopie|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-mikroskopie|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-antigen-antikoerper-quantitativ|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-aviditaet|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-ct-wert|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-titer|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-nugent-score|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-bartlett-score|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-molekulare-pathogenlast|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-resistenzmechanismen-determinanten|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-virulenzfaktor|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-resistenzkategorie-status|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-mrgn-klasse|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-voraussichtliche-empfindlichkeit)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-allgemeine-kultur|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-allgemeine-bestimmung|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-bestimmung|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-keimzahl|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-empfindlichkeit|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-mikroskopie|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-spezifische-mikroskopie|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-antigen-antikoerper-quantitativ|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-aviditaet|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-ct-wert|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-titer|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-nugent-score|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-bartlett-score|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-molekulare-pathogenlast|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-resistenzmechanismen-determinanten|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-virulenzfaktor|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-resistenzkategorie-status|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-mrgn-klasse|https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-voraussichtliche-empfindlichkeit)
 </t>
   </si>
   <si>

--- a/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
